--- a/trading-system/Strategy_Audit_Report.xlsx
+++ b/trading-system/Strategy_Audit_Report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,258 +449,202 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Calmar Ratio</t>
+          <t>Total Trades</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Total Trades</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deterministic Consistency</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Iterations Tested</t>
+          <t>Error</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>advanced_ai</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
+        <v>5850.068586501962</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="E2" t="n">
-        <v>1.26</v>
+        <v>7.47</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>12.06</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100.00% (Passed)</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>10000</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>buy_the_dip</t>
+          <t>meta_agent_swarm</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
+        <v>4146.689453529572</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="E3" t="n">
-        <v>1.65</v>
+        <v>4.54</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100.00% (Passed)</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>10000</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ema_crossover</t>
+          <t>enhanced_ai</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
+        <v>2968.960232083235</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-3.14</v>
       </c>
       <c r="E4" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100.00% (Passed)</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>10000</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ema_rsi</t>
+          <t>ultra_meta_dip_swarm</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
+        <v>729.7432074371754</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E5" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100.00% (Passed)</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>10000</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>enhanced_ai</t>
+          <t>buy_the_dip</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
+        <v>402.0141074371786</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-2.01</v>
       </c>
       <c r="E6" t="n">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100.00% (Passed)</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>10000</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>meta_agent_swarm</t>
+          <t>ema_rsi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
+        <v>123.7483336527803</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-3.43</v>
       </c>
       <c r="E7" t="n">
-        <v>1.82</v>
+        <v>1.03</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100.00% (Passed)</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>10000</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ultra_meta_dip_swarm</t>
+          <t>ema_crossover</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -708,17 +652,7 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100.00% (Passed)</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -729,14 +663,16 @@
       <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -744,53 +680,91 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100.00% (Passed)</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>premium</t>
+          <t>marl_strategy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
+        <v>-727.116143074818</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-2.26</v>
       </c>
       <c r="E10" t="n">
-        <v>1.29</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-2.15</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100.00% (Passed)</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>10000</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>drl_strategy</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-813.1686558109795</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>advanced_ai</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-1202.799876473815</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
